--- a/backend/data/financials_by_company/1427.HK.xlsx
+++ b/backend/data/financials_by_company/1427.HK.xlsx
@@ -4170,7 +4170,7 @@
         <v>-123879000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>0.802</v>
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
         <v>0.039499998</v>
